--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HESTIA MENORCA.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_HESTIA MENORCA.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>87.4507</v>
+        <v>93.48910000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>76.5496</v>
+        <v>83.1216</v>
       </c>
       <c r="F2" t="n">
-        <v>10.9013</v>
+        <v>10.3679</v>
       </c>
       <c r="G2" t="n">
         <v>64.15689999999999</v>
@@ -610,13 +610,13 @@
         <v>42.6314</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5580000000000004</v>
+        <v>5.4806</v>
       </c>
       <c r="T2" t="n">
-        <v>-7.164</v>
+        <v>-0.5922000000000003</v>
       </c>
       <c r="U2" t="n">
-        <v>6.6063</v>
+        <v>6.0727</v>
       </c>
       <c r="V2" t="n">
         <v>29.5069</v>
@@ -643,13 +643,13 @@
         <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>74.7239</v>
+        <v>66.5625</v>
       </c>
       <c r="E3" t="n">
-        <v>37.4471</v>
+        <v>29.1773</v>
       </c>
       <c r="F3" t="n">
-        <v>37.2768</v>
+        <v>37.3855</v>
       </c>
       <c r="G3" t="n">
         <v>5.133599999999999</v>
@@ -688,13 +688,13 @@
         <v>62.4243</v>
       </c>
       <c r="S3" t="n">
-        <v>27.2268</v>
+        <v>19.0651</v>
       </c>
       <c r="T3" t="n">
-        <v>19.2146</v>
+        <v>10.9443</v>
       </c>
       <c r="U3" t="n">
-        <v>8.012499999999999</v>
+        <v>8.121</v>
       </c>
       <c r="V3" t="n">
         <v>0.3845999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>14.0005</v>
+        <v>31.0393</v>
       </c>
       <c r="E4" t="n">
-        <v>32.9232</v>
+        <v>25.6725</v>
       </c>
       <c r="F4" t="n">
-        <v>-18.9227</v>
+        <v>5.367299999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>10.0798</v>
+        <v>7.268000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>3.416500000000001</v>
+        <v>-11.3947</v>
       </c>
       <c r="I4" t="n">
-        <v>6.662899999999999</v>
+        <v>18.663</v>
       </c>
       <c r="J4" t="n">
-        <v>33.3713</v>
+        <v>40.1083</v>
       </c>
       <c r="K4" t="n">
-        <v>17.4563</v>
+        <v>10.8901</v>
       </c>
       <c r="L4" t="n">
-        <v>15.9145</v>
+        <v>29.218</v>
       </c>
       <c r="M4" t="n">
-        <v>-23.2916</v>
+        <v>-32.8399</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.0397</v>
+        <v>-22.2851</v>
       </c>
       <c r="O4" t="n">
-        <v>-9.2517</v>
+        <v>-10.5553</v>
       </c>
       <c r="P4" t="n">
-        <v>11.0928</v>
+        <v>1.0876</v>
       </c>
       <c r="Q4" t="n">
-        <v>-30.4508</v>
+        <v>-58.7266</v>
       </c>
       <c r="R4" t="n">
-        <v>41.5435</v>
+        <v>59.8144</v>
       </c>
       <c r="S4" t="n">
-        <v>18.1044</v>
+        <v>0.4615999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>15.6717</v>
+        <v>2.0709</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4323</v>
+        <v>-1.6099</v>
       </c>
       <c r="V4" t="n">
-        <v>-25.276</v>
+        <v>22.222</v>
       </c>
       <c r="W4" t="n">
-        <v>14.3312</v>
+        <v>42.2203</v>
       </c>
       <c r="X4" t="n">
-        <v>-39.6076</v>
+        <v>-19.9979</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>11.5976</v>
+        <v>12.9668</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.730899999999999</v>
+        <v>-3.722500000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>19.3284</v>
+        <v>16.6888</v>
       </c>
       <c r="G5" t="n">
         <v>-7.015499999999999</v>
@@ -844,13 +844,13 @@
         <v>45.0242</v>
       </c>
       <c r="S5" t="n">
-        <v>6.109100000000001</v>
+        <v>7.4783</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.3714</v>
+        <v>0.6372</v>
       </c>
       <c r="U5" t="n">
-        <v>9.480700000000001</v>
+        <v>6.841</v>
       </c>
       <c r="V5" t="n">
         <v>-8.5944</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>7.9301</v>
+        <v>7.028199999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>18.5705</v>
+        <v>24.0907</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.6399</v>
+        <v>-17.063</v>
       </c>
       <c r="G6" t="n">
-        <v>6.8551</v>
+        <v>10.0798</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3175000000000008</v>
+        <v>3.416500000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>6.5374</v>
+        <v>6.662899999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>22.8354</v>
+        <v>33.3713</v>
       </c>
       <c r="K6" t="n">
-        <v>11.6066</v>
+        <v>17.4563</v>
       </c>
       <c r="L6" t="n">
-        <v>11.2288</v>
+        <v>15.9145</v>
       </c>
       <c r="M6" t="n">
-        <v>-15.9803</v>
+        <v>-23.2916</v>
       </c>
       <c r="N6" t="n">
-        <v>-11.2889</v>
+        <v>-14.0397</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.6915</v>
+        <v>-9.2517</v>
       </c>
       <c r="P6" t="n">
-        <v>16.7476</v>
+        <v>11.0928</v>
       </c>
       <c r="Q6" t="n">
-        <v>-20.0103</v>
+        <v>-30.4508</v>
       </c>
       <c r="R6" t="n">
-        <v>36.7581</v>
+        <v>41.5435</v>
       </c>
       <c r="S6" t="n">
-        <v>11.7015</v>
+        <v>11.1317</v>
       </c>
       <c r="T6" t="n">
-        <v>8.8833</v>
+        <v>6.839</v>
       </c>
       <c r="U6" t="n">
-        <v>2.8181</v>
+        <v>4.2929</v>
       </c>
       <c r="V6" t="n">
-        <v>-27.3742</v>
+        <v>-25.276</v>
       </c>
       <c r="W6" t="n">
-        <v>6.8625</v>
+        <v>14.3312</v>
       </c>
       <c r="X6" t="n">
-        <v>-34.2369</v>
+        <v>-39.6076</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>6.081</v>
+        <v>4.442699999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>12.7729</v>
+        <v>14.9798</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.6916</v>
+        <v>-10.5373</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7167</v>
+        <v>6.8551</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3439</v>
+        <v>0.3175000000000008</v>
       </c>
       <c r="I7" t="n">
-        <v>6.060599999999999</v>
+        <v>6.5374</v>
       </c>
       <c r="J7" t="n">
-        <v>19.2329</v>
+        <v>22.8354</v>
       </c>
       <c r="K7" t="n">
-        <v>6.5141</v>
+        <v>11.6066</v>
       </c>
       <c r="L7" t="n">
-        <v>12.7183</v>
+        <v>11.2288</v>
       </c>
       <c r="M7" t="n">
-        <v>-15.5158</v>
+        <v>-15.9803</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.857699999999999</v>
+        <v>-11.2889</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.6581</v>
+        <v>-4.6915</v>
       </c>
       <c r="P7" t="n">
-        <v>8.917399999999999</v>
+        <v>16.7476</v>
       </c>
       <c r="Q7" t="n">
-        <v>-20.4452</v>
+        <v>-20.0103</v>
       </c>
       <c r="R7" t="n">
-        <v>29.3628</v>
+        <v>36.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>17.2434</v>
+        <v>8.214</v>
       </c>
       <c r="T7" t="n">
-        <v>14.0358</v>
+        <v>5.2926</v>
       </c>
       <c r="U7" t="n">
-        <v>3.2076</v>
+        <v>2.9214</v>
       </c>
       <c r="V7" t="n">
-        <v>-23.7968</v>
+        <v>-27.3742</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.05050000000000016</v>
+        <v>6.8625</v>
       </c>
       <c r="X7" t="n">
-        <v>-23.7464</v>
+        <v>-34.2369</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>T. MCFADDEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>2.777000000000001</v>
+        <v>0.9267000000000003</v>
       </c>
       <c r="E8" t="n">
-        <v>7.593</v>
+        <v>-5.4516</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.815999999999999</v>
+        <v>6.378200000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>7.268000000000001</v>
+        <v>0.7010000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-11.3947</v>
+        <v>3.1896</v>
       </c>
       <c r="I8" t="n">
-        <v>18.663</v>
+        <v>-2.488899999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>40.1083</v>
+        <v>11.4466</v>
       </c>
       <c r="K8" t="n">
-        <v>10.8901</v>
+        <v>9.507899999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>29.218</v>
+        <v>1.938600000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-32.8399</v>
+        <v>-10.7457</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.2851</v>
+        <v>-6.318099999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-10.5553</v>
+        <v>-4.4276</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0876</v>
+        <v>-6.742800000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-58.7266</v>
+        <v>-28.9283</v>
       </c>
       <c r="R8" t="n">
-        <v>59.8144</v>
+        <v>22.1858</v>
       </c>
       <c r="S8" t="n">
-        <v>-27.8006</v>
+        <v>-3.9553</v>
       </c>
       <c r="T8" t="n">
-        <v>-16.0082</v>
+        <v>-3.2867</v>
       </c>
       <c r="U8" t="n">
-        <v>-11.7919</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>22.222</v>
+        <v>10.924</v>
       </c>
       <c r="W8" t="n">
-        <v>42.2203</v>
+        <v>15.3166</v>
       </c>
       <c r="X8" t="n">
-        <v>-19.9979</v>
+        <v>-4.3926</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1307</v>
+        <v>-1.0999</v>
       </c>
       <c r="E9" t="n">
         <v>-1.1178</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0129</v>
+        <v>0.0179</v>
       </c>
       <c r="G9" t="n">
         <v>0.1538</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.197</v>
+        <v>-0.1661</v>
       </c>
       <c r="T9" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.372</v>
+        <v>-1.2602</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2245</v>
+        <v>-1.1128</v>
       </c>
       <c r="F10" t="n">
         <v>-0.1475</v>
@@ -1234,10 +1234,10 @@
         <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. ROTEGARD</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.773099999999999</v>
+        <v>-2.663399999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0653</v>
+        <v>11.5918</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7079</v>
+        <v>-14.2549</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5609</v>
+        <v>-9.2788</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7418</v>
+        <v>-7.616199999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8191000000000002</v>
+        <v>-1.662300000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6972</v>
+        <v>13.7007</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5626</v>
+        <v>1.7403</v>
       </c>
       <c r="L11" t="n">
-        <v>2.2598</v>
+        <v>11.9601</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1364000000000001</v>
+        <v>-22.9797</v>
       </c>
       <c r="N11" t="n">
-        <v>1.3044</v>
+        <v>-9.357000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4407</v>
+        <v>-13.6227</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2175</v>
+        <v>-1.3051</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3925</v>
+        <v>-31.756</v>
       </c>
       <c r="R11" t="n">
-        <v>2.175</v>
+        <v>30.4505</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4013</v>
+        <v>-1.4826</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.37</v>
+        <v>-0.1850000000000002</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0316</v>
+        <v>-1.2979</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.7151</v>
+        <v>9.4031</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>29.8317</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.7151</v>
+        <v>-20.4288</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. ROSA POMPIDO</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4543</v>
+        <v>-3.063800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.769</v>
+        <v>5.425400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6852</v>
+        <v>-8.489599999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6769</v>
+        <v>3.7167</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1685</v>
+        <v>-2.3439</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5083</v>
+        <v>6.060599999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4297</v>
+        <v>19.2329</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0887</v>
+        <v>6.5141</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3411</v>
+        <v>12.7183</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2472</v>
+        <v>-15.5158</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.08</v>
+        <v>-8.857699999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1675</v>
+        <v>-6.6581</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5225</v>
+        <v>8.917399999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.2625</v>
+        <v>-20.4452</v>
       </c>
       <c r="R12" t="n">
-        <v>1.74</v>
+        <v>29.3628</v>
       </c>
       <c r="S12" t="n">
-        <v>0.07029999999999997</v>
+        <v>8.0985</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.07690000000000002</v>
+        <v>6.689</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1471</v>
+        <v>1.4097</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3252</v>
+        <v>-23.7968</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.05050000000000016</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.3252</v>
+        <v>-23.7464</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. MCFADDEN</t>
+          <t>T. ROTEGARD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.020700000000001</v>
+        <v>-4.5364</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.8367</v>
+        <v>-1.0342</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8159</v>
+        <v>-3.5023</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7010000000000001</v>
+        <v>1.5609</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1896</v>
+        <v>0.7418</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.488899999999998</v>
+        <v>0.8191000000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>11.4466</v>
+        <v>1.6972</v>
       </c>
       <c r="K13" t="n">
-        <v>9.507899999999999</v>
+        <v>-0.5626</v>
       </c>
       <c r="L13" t="n">
-        <v>1.938600000000001</v>
+        <v>2.2598</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.7457</v>
+        <v>-0.1364000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.318099999999999</v>
+        <v>1.3044</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.4276</v>
+        <v>-1.4407</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.742800000000001</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q13" t="n">
-        <v>-28.9283</v>
+        <v>-2.3925</v>
       </c>
       <c r="R13" t="n">
-        <v>22.1858</v>
+        <v>2.175</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.9025</v>
+        <v>-1.1648</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.6716</v>
+        <v>-0.3389</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.2311</v>
+        <v>-0.826</v>
       </c>
       <c r="V13" t="n">
-        <v>10.924</v>
+        <v>-4.7151</v>
       </c>
       <c r="W13" t="n">
-        <v>15.3166</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.3926</v>
+        <v>-4.7151</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>P. FIGUERAS LOPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.2798</v>
+        <v>-6.4906</v>
       </c>
       <c r="E14" t="n">
-        <v>2.808900000000001</v>
+        <v>-8.7775</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.0883</v>
+        <v>2.2868</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9438</v>
+        <v>-4.065700000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7395</v>
+        <v>-0.8209999999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2045999999999999</v>
+        <v>-3.2447</v>
       </c>
       <c r="J14" t="n">
-        <v>11.9452</v>
+        <v>1.323500000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.0294</v>
+        <v>2.0938</v>
       </c>
       <c r="L14" t="n">
-        <v>4.9154</v>
+        <v>-0.7705000000000006</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.0017</v>
+        <v>-5.3891</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.290500000000001</v>
+        <v>-2.9149</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.7114</v>
+        <v>-2.4743</v>
       </c>
       <c r="P14" t="n">
-        <v>-13.268</v>
+        <v>-6.090199999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-37.6284</v>
+        <v>-14.3555</v>
       </c>
       <c r="R14" t="n">
-        <v>24.3603</v>
+        <v>8.2653</v>
       </c>
       <c r="S14" t="n">
-        <v>13.5239</v>
+        <v>1.1053</v>
       </c>
       <c r="T14" t="n">
-        <v>14.8494</v>
+        <v>0.2788</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.326</v>
+        <v>0.8265</v>
       </c>
       <c r="V14" t="n">
-        <v>-12.4793</v>
+        <v>2.5598</v>
       </c>
       <c r="W14" t="n">
-        <v>13.6425</v>
+        <v>3.9755</v>
       </c>
       <c r="X14" t="n">
-        <v>-26.1218</v>
+        <v>-1.4157</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. FIGUERAS LOPEZ</t>
+          <t>I. ROSA POMPIDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-10.9046</v>
+        <v>-6.5237</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.051</v>
+        <v>-4.9925</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1464</v>
+        <v>-1.5311</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.065700000000001</v>
+        <v>-3.6769</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8209999999999998</v>
+        <v>-2.1685</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.2447</v>
+        <v>-1.5083</v>
       </c>
       <c r="J15" t="n">
-        <v>1.323500000000001</v>
+        <v>-1.4297</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0938</v>
+        <v>-1.0887</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7705000000000006</v>
+        <v>-0.3411</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.3891</v>
+        <v>-2.2472</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.9149</v>
+        <v>-1.08</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.4743</v>
+        <v>-1.1675</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.090199999999999</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q15" t="n">
-        <v>-14.3555</v>
+        <v>-3.2625</v>
       </c>
       <c r="R15" t="n">
-        <v>8.2653</v>
+        <v>1.74</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.3086</v>
+        <v>0.001000000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.9946</v>
+        <v>-0.3004000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3141</v>
+        <v>0.3013</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5598</v>
+        <v>-1.3252</v>
       </c>
       <c r="W15" t="n">
-        <v>3.9755</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4157</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>18</v>
       </c>
       <c r="D16" t="n">
-        <v>-16.8492</v>
+        <v>-15.2019</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.882</v>
+        <v>-11.3785</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.9676</v>
+        <v>-3.8236</v>
       </c>
       <c r="G16" t="n">
         <v>-9.1126</v>
@@ -1702,13 +1702,13 @@
         <v>7.1776</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1713000000000001</v>
+        <v>1.476</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9122000000000001</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7407999999999999</v>
+        <v>0.8847</v>
       </c>
       <c r="V16" t="n">
         <v>-3.2153</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>-17.584</v>
+        <v>-18.5764</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4117</v>
+        <v>-7.235</v>
       </c>
       <c r="F17" t="n">
-        <v>-20.9954</v>
+        <v>-11.341</v>
       </c>
       <c r="G17" t="n">
-        <v>-9.2788</v>
+        <v>1.9438</v>
       </c>
       <c r="H17" t="n">
-        <v>-7.616199999999999</v>
+        <v>1.7395</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.662300000000001</v>
+        <v>0.2045999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>13.7007</v>
+        <v>11.9452</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7403</v>
+        <v>7.0294</v>
       </c>
       <c r="L17" t="n">
-        <v>11.9601</v>
+        <v>4.9154</v>
       </c>
       <c r="M17" t="n">
-        <v>-22.9797</v>
+        <v>-10.0017</v>
       </c>
       <c r="N17" t="n">
-        <v>-9.357000000000001</v>
+        <v>-5.290500000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-13.6227</v>
+        <v>-4.7114</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3051</v>
+        <v>-13.268</v>
       </c>
       <c r="Q17" t="n">
-        <v>-31.756</v>
+        <v>-37.6284</v>
       </c>
       <c r="R17" t="n">
-        <v>30.4505</v>
+        <v>24.3603</v>
       </c>
       <c r="S17" t="n">
-        <v>-16.4029</v>
+        <v>5.2269</v>
       </c>
       <c r="T17" t="n">
-        <v>-8.365</v>
+        <v>4.806</v>
       </c>
       <c r="U17" t="n">
-        <v>-8.038</v>
+        <v>0.4212000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>9.4031</v>
+        <v>-12.4793</v>
       </c>
       <c r="W17" t="n">
-        <v>29.8317</v>
+        <v>13.6425</v>
       </c>
       <c r="X17" t="n">
-        <v>-20.4288</v>
+        <v>-26.1218</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>-31.4498</v>
+        <v>-20.44</v>
       </c>
       <c r="E18" t="n">
-        <v>-25.7026</v>
+        <v>-18.8133</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.7471</v>
+        <v>-1.6268</v>
       </c>
       <c r="G18" t="n">
         <v>10.1943</v>
@@ -1858,13 +1858,13 @@
         <v>36.1056</v>
       </c>
       <c r="S18" t="n">
-        <v>-10.6731</v>
+        <v>0.3366000000000002</v>
       </c>
       <c r="T18" t="n">
-        <v>-5.3259</v>
+        <v>1.5637</v>
       </c>
       <c r="U18" t="n">
-        <v>-5.347</v>
+        <v>-1.2268</v>
       </c>
       <c r="V18" t="n">
         <v>-7.0452</v>
@@ -1891,13 +1891,13 @@
         <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>95.74259999999997</v>
+        <v>136.599</v>
       </c>
       <c r="E19" t="n">
-        <v>115.6971</v>
+        <v>130.4234</v>
       </c>
       <c r="F19" t="n">
-        <v>-19.9533</v>
+        <v>6.175299999999996</v>
       </c>
       <c r="G19" t="n">
         <v>78.24939999999998</v>
@@ -1927,7 +1927,7 @@
         <v>-84.7516</v>
       </c>
       <c r="P19" t="n">
-        <v>35.8877</v>
+        <v>35.88769999999999</v>
       </c>
       <c r="Q19" t="n">
         <v>-414.3475</v>
@@ -1936,16 +1936,16 @@
         <v>450.2363</v>
       </c>
       <c r="S19" t="n">
-        <v>20.42710000000002</v>
+        <v>61.2816</v>
       </c>
       <c r="T19" t="n">
-        <v>20.18950000000001</v>
+        <v>34.9158</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2371999999999996</v>
+        <v>26.3653</v>
       </c>
       <c r="V19" t="n">
-        <v>-38.82110000000001</v>
+        <v>-38.8211</v>
       </c>
       <c r="W19" t="n">
         <v>210.1615</v>
